--- a/docs/deliverables/out/Drop-2_Independent/TestPlans/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-2_Independent/TestPlans/BIBS_TestPlan_BRD-07_Claims_v1.0.xlsx
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
